--- a/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45775</t>
+          <t>45320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45552</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>70603</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52598</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70388</t>
+          <t>69763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>43943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72251</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102014</t>
+          <t>100323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136287</t>
+          <t>135412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>55386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66098</t>
+          <t>66975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>12548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24708</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>43895</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50030</t>
+          <t>49776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52898</t>
+          <t>50838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82276</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>87450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123291</t>
+          <t>121221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80789</t>
+          <t>81681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>106653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107510</t>
+          <t>109856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137998</t>
+          <t>140251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199194</t>
+          <t>199611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239709</t>
+          <t>239061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23938</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51612</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>40736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>52188</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84573</t>
+          <t>84813</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42297</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57991</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92420</t>
+          <t>93245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>44590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>94653</t>
+          <t>93374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>57928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>85454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115893</t>
+          <t>118505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166936</t>
+          <t>170624</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105520</t>
+          <t>117200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46145</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>67388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152231</t>
+          <t>155114</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20706</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25898</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29606</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44910</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>69146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52104</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>61404</t>
+          <t>60956</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>87348</t>
+          <t>88671</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>69398</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>90740</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>85364</t>
+          <t>84547</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>137707</t>
+          <t>136504</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>168863</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>37085</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33751</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55226</t>
+          <t>55543</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>131762</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>105673</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,47 +4151,47 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>184903</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>164197</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>184903</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>160068</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>208894</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>277124</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>340459</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>267540</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>338461</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>589720</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>677064</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100131</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>214550</t>
+          <t>210399</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>142995</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>201674</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>324572</t>
+          <t>316091</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>66370</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1046</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7305</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15911</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9324</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24695</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12384</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8487</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18145</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>28780</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19787</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34672</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25310</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>45843</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27,63%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22436</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15926</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30593</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>17603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>34849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>47101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70603</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49420</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37069</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60591</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61573</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52285</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>69763</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>63645</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43943</t>
+          <t>53798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>120470</t>
+          <t>113065</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100323</t>
+          <t>95671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135412</t>
+          <t>127989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22288</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12245</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43617</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10079</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>31459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66975</t>
+          <t>58312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4644</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>125488</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116901</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>120745</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>120745</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>120745</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>139883</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>139883</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>139883</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>365</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256783</t>
+          <t>246233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6033</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19061</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12785</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27975</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14345</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8991</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21245</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>21370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61393</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49022</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77294</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>38841</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29678</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>49776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50838</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80920</t>
+          <t>53020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103657</t>
+          <t>102251</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87450</t>
+          <t>86720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121221</t>
+          <t>122164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119066</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>104408</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133509</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>95301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81681</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>50,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>42,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123763</t>
+          <t>95648</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109856</t>
+          <t>83841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140251</t>
+          <t>107601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>219065</t>
+          <t>214715</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199611</t>
+          <t>195828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239061</t>
+          <t>233429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24011</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32309</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>34144</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>23938</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>50559</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,92%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30523</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>34442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64666</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>52188</t>
+          <t>40657</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84813</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5049</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14720</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5906</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10599</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>235921</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>184413</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>184413</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>184413</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>253707</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>253707</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>253707</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>621</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>444220</t>
+          <t>420334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2769</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5263</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22806</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14836</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>33480</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>11193</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5622</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23962</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40331</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>30363</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>53832</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>31100</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>19394</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42430</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74926</t>
+          <t>71714</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>58375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93245</t>
+          <t>88138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65580</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>52234</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78253</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>75611</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44590</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>93374</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>39,88%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>49,25%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71026</t>
+          <t>74872</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85454</t>
+          <t>85551</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>146637</t>
+          <t>140453</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118505</t>
+          <t>124188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170624</t>
+          <t>157160</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>29023</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>21351</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>39166</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12,83%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>59729</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33654</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>117200</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>39897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>58674</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>47319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155114</t>
+          <t>72609</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>156204</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>156204</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>156204</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>182868</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>182868</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>182868</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>446</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>322647</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7316</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4349</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1769</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8089</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>36541</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>27265</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>45845</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>16,1%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>17924</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12262</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>25898</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>44910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69146</t>
+          <t>67717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>38369</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>28772</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>48634</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>28,71%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>33048</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>25500</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>41648</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>34372</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52657</t>
+          <t>43959</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>72741</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>60956</t>
+          <t>60949</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>88671</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>67664</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>56074</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>78779</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>39,95%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>79822</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>68855</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>90785</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>47,85%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>41,27%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>54,42%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>80189</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>61968</t>
+          <t>69699</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>84547</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>153269</t>
+          <t>147854</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>130410</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>168863</t>
+          <t>164034</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>15971</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>10633</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>22872</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>26956</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>18895</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>37085</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>32190</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55543</t>
+          <t>51022</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7443</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>12997</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>4731</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>9402</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>166831</t>
+          <t>169376</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>166160</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>348069</t>
+          <t>335536</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>17625</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>21777</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>18889</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>34831</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>28225</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>37083</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>174766</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>152743</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>199469</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>125424</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>105673</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>145262</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>184903</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>164197</t>
+          <t>114351</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>211456</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277124</t>
+          <t>277603</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>340671</t>
+          <t>337157</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>301731</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>277875</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>327411</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>312307</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>268662</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>339342</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>51,12%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>300735</t>
+          <t>293352</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>354232</t>
+          <t>336033</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>639441</t>
+          <t>616087</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>589720</t>
+          <t>582175</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>678934</t>
+          <t>648423</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -4352,57 +4352,57 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>91293</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>76625</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>120786</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>100131</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>210399</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>89148</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>104111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>238583</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>200740</t>
+          <t>159353</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>316091</t>
+          <t>211488</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>24051</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>17939</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>33343</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>24488</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>18261</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>33730</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>38154</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1908</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">

--- a/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Habitat-trans_orig.xlsx
@@ -1007,7 +1007,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1508,7 +1508,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2009,7 +2009,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2510,7 +2510,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -3011,7 +3011,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
